--- a/Data/Suivi_Démarche_questionnaires_Janvier2026.xlsx
+++ b/Data/Suivi_Démarche_questionnaires_Janvier2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFFEDE1A-0C44-4E97-96D3-AC17A118D803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02E5E763-E7C5-44DC-89D2-5F6E99C0ADEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="247">
   <si>
     <t>1.2 Incertitudes</t>
   </si>
@@ -609,6 +609,233 @@
   </si>
   <si>
     <t>ROTATIONS_CULTURE_FRANCE</t>
+  </si>
+  <si>
+    <t>DATA TABLEUR</t>
+  </si>
+  <si>
+    <t>source: url Knowledge4policy
+Stockage disque PC</t>
+  </si>
+  <si>
+    <t>peu d'éléments</t>
+  </si>
+  <si>
+    <t>https://soilgrids.org</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DATA  </t>
+  </si>
+  <si>
+    <t>Thésaurus INRAE
+Diverses réponses (mais pas les références :(</t>
+  </si>
+  <si>
+    <t>Pas d'infos
+Ne sait pas où elles sont stockées</t>
+  </si>
+  <si>
+    <t>visualisation et croisement de BDD?
+Pas de lien, ni ref</t>
+  </si>
+  <si>
+    <t>peu de chose</t>
+  </si>
+  <si>
+    <t>PACKAGE</t>
+  </si>
+  <si>
+    <t>article de recherche associé? Lequel?</t>
+  </si>
+  <si>
+    <t>pas de ref, pas d'infos</t>
+  </si>
+  <si>
+    <t>but: obtention de la BDD
+Lien Github
+objectif décrit</t>
+  </si>
+  <si>
+    <t>Infos utiles à peu près ok</t>
+  </si>
+  <si>
+    <t>Diverses réponses mais pas de ref</t>
+  </si>
+  <si>
+    <t>Un data paper?</t>
+  </si>
+  <si>
+    <t>contact, forge, description</t>
+  </si>
+  <si>
+    <t>infos utiles ok</t>
+  </si>
+  <si>
+    <t>PACKAGE INDIVIDUEL</t>
+  </si>
+  <si>
+    <t>DONNEES UTILES ESTIMATION POTENTIELS ENERGETIQUES</t>
+  </si>
+  <si>
+    <t>"plein" de sources, mais lesquelles?
+"Plusieurs ref" mais lesquelles</t>
+  </si>
+  <si>
+    <t>Volonté de réponse ok mais pas de docs, lien…</t>
+  </si>
+  <si>
+    <t>ENREGISTREMENTS DES ATELIERS</t>
+  </si>
+  <si>
+    <t>FICHES HYPOTHESES</t>
+  </si>
+  <si>
+    <t>COMPTE-RENDU ENTRETIENS</t>
+  </si>
+  <si>
+    <t>DATA AUDIO</t>
+  </si>
+  <si>
+    <t>DATA IMAGE</t>
+  </si>
+  <si>
+    <t>DATA TEXTE</t>
+  </si>
+  <si>
+    <t>atelier</t>
+  </si>
+  <si>
+    <t>entretiens</t>
+  </si>
+  <si>
+    <t>questionnement Anonymisation et quel partage?</t>
+  </si>
+  <si>
+    <t>idem</t>
+  </si>
+  <si>
+    <t>MATERIAUX ENTRETIENS SUPPLEMENTAIRES</t>
+  </si>
+  <si>
+    <t>DATA SHS</t>
+  </si>
+  <si>
+    <t>sensibilité éthique, données personnelles</t>
+  </si>
+  <si>
+    <t>peu d'infos mais réponse ok</t>
+  </si>
+  <si>
+    <t>REGISTRE PARCELLAIRE GRAPHIQUE</t>
+  </si>
+  <si>
+    <t>source ign</t>
+  </si>
+  <si>
+    <t>DATA SHAPE</t>
+  </si>
+  <si>
+    <t>ANALYSES DE SOL</t>
+  </si>
+  <si>
+    <t>DATA IN SITU</t>
+  </si>
+  <si>
+    <t>Data paper (à venir?)</t>
+  </si>
+  <si>
+    <t>réponse ok, droits réservés?</t>
+  </si>
+  <si>
+    <t>stockage entrepot PO2?</t>
+  </si>
+  <si>
+    <t>avec PO2Manager
+Base Phylis</t>
+  </si>
+  <si>
+    <t>FAIRCARBON SLAM-B PROPOSAL</t>
+  </si>
+  <si>
+    <t>SCENARIO LABS INFO</t>
+  </si>
+  <si>
+    <t>SYS-METHA MODEL AND PROCESS SCENARIO DATA</t>
+  </si>
+  <si>
+    <t>SYS-METHA FEEDSTOCK DATABASE</t>
+  </si>
+  <si>
+    <t>usage privé?</t>
+  </si>
+  <si>
+    <t>source: project PI?</t>
+  </si>
+  <si>
+    <t>Conditions de réutilisations inconnues?</t>
+  </si>
+  <si>
+    <t>DOI + ref OK</t>
+  </si>
+  <si>
+    <t>source: shared drive? Stockage Cloud INRAE?</t>
+  </si>
+  <si>
+    <t>droits réservés</t>
+  </si>
+  <si>
+    <t>ne connais pas la source, transmis par les membres du projet</t>
+  </si>
+  <si>
+    <t>SYS-METHA SOLVER (EXCEL BASED)</t>
+  </si>
+  <si>
+    <t>MODIFIED ADM1 BASED SOLVER FOR AD DYNAMICS PREDICTIONS</t>
+  </si>
+  <si>
+    <t>AD PROCESS CHAIN MODEL FRAMEWORK (PSEUDO-DYNAMIC)</t>
+  </si>
+  <si>
+    <t>un article de ref 2001 ok</t>
+  </si>
+  <si>
+    <t>PACKAGE COLLECTIF</t>
+  </si>
+  <si>
+    <t>beaucoup d'inconnues, mais un article de ref</t>
+  </si>
+  <si>
+    <t>volonté de réponse</t>
+  </si>
+  <si>
+    <t>pas clair</t>
+  </si>
+  <si>
+    <t>AD PROCESS CHAIN OPTIMIZER</t>
+  </si>
+  <si>
+    <t>peu d'infos</t>
+  </si>
+  <si>
+    <t>AD RESULTS</t>
+  </si>
+  <si>
+    <t>MODIFIED ADM1 AND SYS-METHA SIMULATION DATA</t>
+  </si>
+  <si>
+    <t>STABILIZATION TIMES OF AD PROCESS VARIABLES</t>
+  </si>
+  <si>
+    <t>SCENARIO FOR AD PROCESS CHAIN MODEL SIMULATION AND OPTIMIZATION</t>
+  </si>
+  <si>
+    <t>DATA FICTIVES</t>
+  </si>
+  <si>
+    <t>RETRANSCRIPTIONS D'ENTRETIENS SEMI-DIRECTIFS</t>
+  </si>
+  <si>
+    <t>AGENT FORESTIER</t>
   </si>
 </sst>
 </file>
@@ -676,7 +903,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -737,8 +964,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="29">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -1070,32 +1303,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -1112,15 +1319,6 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -1129,7 +1327,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1188,231 +1386,314 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="22" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -2571,7 +2852,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8F21098-E3BE-45B2-A2ED-20BD6F5C323A}">
-  <dimension ref="B1:J57"/>
+  <dimension ref="B1:J55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="19.26953125" customWidth="1"/>
@@ -2586,78 +2867,78 @@
   <sheetData>
     <row r="1" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="B2" s="75"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76" t="s">
+      <c r="B2" s="83"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84" t="s">
         <v>122</v>
       </c>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="77"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="87"/>
     </row>
     <row r="3" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="B3" s="78" t="s">
+      <c r="B3" s="88" t="s">
         <v>123</v>
       </c>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79" t="s">
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85" t="s">
         <v>124</v>
       </c>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="80"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="89"/>
     </row>
     <row r="4" spans="2:10" ht="19" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="85" t="s">
+      <c r="B4" s="69" t="s">
         <v>125</v>
       </c>
-      <c r="C4" s="86" t="s">
+      <c r="C4" s="70" t="s">
         <v>127</v>
       </c>
-      <c r="D4" s="86" t="s">
+      <c r="D4" s="70" t="s">
         <v>126</v>
       </c>
-      <c r="E4" s="86" t="s">
+      <c r="E4" s="70" t="s">
         <v>164</v>
       </c>
-      <c r="F4" s="87"/>
-      <c r="G4" s="86" t="s">
+      <c r="F4" s="90"/>
+      <c r="G4" s="70" t="s">
         <v>125</v>
       </c>
-      <c r="H4" s="86" t="s">
+      <c r="H4" s="70" t="s">
         <v>127</v>
       </c>
-      <c r="I4" s="86" t="s">
+      <c r="I4" s="70" t="s">
         <v>126</v>
       </c>
-      <c r="J4" s="88" t="s">
+      <c r="J4" s="71" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B5" s="25"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="27" t="s">
+      <c r="B5" s="23"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="80" t="s">
         <v>79</v>
       </c>
-      <c r="G5" s="28" t="s">
+      <c r="G5" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="I5" s="29" t="s">
+      <c r="I5" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="J5" s="30" t="s">
+      <c r="J5" s="27" t="s">
         <v>131</v>
       </c>
     </row>
@@ -2666,91 +2947,91 @@
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="16"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="32" t="s">
+      <c r="F6" s="81"/>
+      <c r="G6" s="28" t="s">
         <v>132</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="I6" s="33" t="s">
+      <c r="I6" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="J6" s="34" t="s">
+      <c r="J6" s="30" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="7" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B7" s="36"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="27" t="s">
+      <c r="B7" s="32"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="80" t="s">
         <v>80</v>
       </c>
-      <c r="G7" s="37" t="s">
+      <c r="G7" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="H7" s="28" t="s">
+      <c r="H7" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="I7" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="J7" s="30" t="s">
+      <c r="J7" s="27" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="8" spans="2:10" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="47"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="49" t="s">
+      <c r="B8" s="43"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="82"/>
+      <c r="G8" s="45" t="s">
         <v>138</v>
       </c>
-      <c r="H8" s="50" t="s">
+      <c r="H8" s="46" t="s">
         <v>140</v>
       </c>
-      <c r="I8" s="51" t="s">
+      <c r="I8" s="47" t="s">
         <v>141</v>
       </c>
-      <c r="J8" s="52" t="s">
+      <c r="J8" s="48" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="9" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="35" t="s">
         <v>143</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="D9" s="40" t="s">
+      <c r="D9" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="E9" s="40" t="s">
+      <c r="E9" s="36" t="s">
         <v>146</v>
       </c>
-      <c r="F9" s="55" t="s">
+      <c r="F9" s="77" t="s">
         <v>81</v>
       </c>
-      <c r="G9" s="37" t="s">
+      <c r="G9" s="33" t="s">
         <v>149</v>
       </c>
-      <c r="H9" s="26" t="s">
+      <c r="H9" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="I9" s="29" t="s">
+      <c r="I9" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="J9" s="30" t="s">
+      <c r="J9" s="27" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="10" spans="2:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="20" t="s">
         <v>144</v>
       </c>
       <c r="C10" s="6" t="s">
@@ -2762,7 +3043,7 @@
       <c r="E10" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F10" s="21"/>
+      <c r="F10" s="79"/>
       <c r="G10" s="6" t="s">
         <v>150</v>
       </c>
@@ -2777,677 +3058,845 @@
       </c>
     </row>
     <row r="11" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="42"/>
-      <c r="C11" s="38"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="34"/>
       <c r="D11" s="17"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="56"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="78"/>
       <c r="G11" s="16" t="s">
         <v>151</v>
       </c>
       <c r="H11" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="I11" s="53" t="s">
+      <c r="I11" s="49" t="s">
         <v>154</v>
       </c>
-      <c r="J11" s="54" t="s">
+      <c r="J11" s="50" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="12" spans="2:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="57"/>
-      <c r="C12" s="58"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58"/>
-      <c r="F12" s="59" t="s">
+      <c r="B12" s="51"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="G12" s="60" t="s">
+      <c r="G12" s="54" t="s">
         <v>155</v>
       </c>
-      <c r="H12" s="60" t="s">
+      <c r="H12" s="54" t="s">
         <v>156</v>
       </c>
-      <c r="I12" s="58"/>
-      <c r="J12" s="61"/>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B13" s="25"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="55" t="s">
+      <c r="I12" s="95" t="s">
+        <v>218</v>
+      </c>
+      <c r="J12" s="111" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B13" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="D13" s="113" t="s">
+        <v>224</v>
+      </c>
+      <c r="E13" s="113" t="s">
+        <v>223</v>
+      </c>
+      <c r="F13" s="77" t="s">
         <v>83</v>
       </c>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="41"/>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B14" s="23"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="35"/>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B15" s="23"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="35"/>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B16" s="23"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="35"/>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B17" s="23"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="35"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B18" s="23"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="35"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B19" s="23"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="35"/>
-    </row>
-    <row r="20" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="62"/>
-      <c r="C20" s="63"/>
-      <c r="D20" s="63"/>
-      <c r="E20" s="63"/>
-      <c r="F20" s="56"/>
-      <c r="G20" s="63"/>
-      <c r="H20" s="63"/>
-      <c r="I20" s="63"/>
-      <c r="J20" s="64"/>
-    </row>
-    <row r="21" spans="2:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="65"/>
-      <c r="C21" s="66"/>
-      <c r="D21" s="66"/>
-      <c r="E21" s="74" t="s">
+      <c r="G13" s="33" t="s">
+        <v>231</v>
+      </c>
+      <c r="H13" s="33" t="s">
+        <v>192</v>
+      </c>
+      <c r="I13" s="104" t="s">
+        <v>233</v>
+      </c>
+      <c r="J13" s="122" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B14" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>201</v>
+      </c>
+      <c r="D14" s="114" t="s">
+        <v>227</v>
+      </c>
+      <c r="E14" s="115" t="s">
+        <v>223</v>
+      </c>
+      <c r="F14" s="79"/>
+      <c r="G14" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>234</v>
+      </c>
+      <c r="I14" s="116" t="s">
+        <v>237</v>
+      </c>
+      <c r="J14" s="119" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B15" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>174</v>
+      </c>
+      <c r="D15" s="116" t="s">
+        <v>226</v>
+      </c>
+      <c r="E15" s="117" t="s">
+        <v>225</v>
+      </c>
+      <c r="F15" s="79"/>
+      <c r="G15" s="112" t="s">
+        <v>238</v>
+      </c>
+      <c r="H15" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="I15" s="115" t="s">
+        <v>239</v>
+      </c>
+      <c r="J15" s="121"/>
+    </row>
+    <row r="16" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B16" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>174</v>
+      </c>
+      <c r="D16" s="114" t="s">
+        <v>229</v>
+      </c>
+      <c r="E16" s="115" t="s">
+        <v>228</v>
+      </c>
+      <c r="F16" s="79"/>
+      <c r="G16" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="H16" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="I16" s="22"/>
+      <c r="J16" s="31"/>
+    </row>
+    <row r="17" spans="2:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="B17" s="118" t="s">
+        <v>230</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="D17" s="117" t="s">
+        <v>235</v>
+      </c>
+      <c r="E17" s="116" t="s">
+        <v>236</v>
+      </c>
+      <c r="F17" s="79"/>
+      <c r="G17" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="I17" s="120"/>
+      <c r="J17" s="123"/>
+    </row>
+    <row r="18" spans="2:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="B18" s="21"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="79"/>
+      <c r="G18" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="I18" s="120"/>
+      <c r="J18" s="123"/>
+    </row>
+    <row r="19" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B19" s="21"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="79"/>
+      <c r="G19" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="I19" s="10"/>
+      <c r="J19" s="14"/>
+    </row>
+    <row r="20" spans="2:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B20" s="56"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="65" t="s">
         <v>162</v>
       </c>
-      <c r="F21" s="67" t="s">
+      <c r="F20" s="58" t="s">
         <v>84</v>
       </c>
-      <c r="G21" s="66"/>
-      <c r="H21" s="66"/>
-      <c r="I21" s="66"/>
-      <c r="J21" s="74" t="s">
+      <c r="G20" s="57"/>
+      <c r="H20" s="57"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="65" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="22" spans="2:10" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="68" t="s">
+    <row r="21" spans="2:10" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B21" s="59" t="s">
         <v>157</v>
       </c>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="59" t="s">
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="52"/>
+      <c r="F21" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="G22" s="58" t="s">
+      <c r="G21" s="52" t="s">
         <v>158</v>
       </c>
-      <c r="H22" s="58"/>
-      <c r="I22" s="58"/>
-      <c r="J22" s="61"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B23" s="25"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="55" t="s">
+      <c r="H21" s="52"/>
+      <c r="I21" s="52"/>
+      <c r="J21" s="55"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B22" s="23"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="77" t="s">
         <v>86</v>
       </c>
-      <c r="G23" s="37" t="s">
+      <c r="G22" s="33" t="s">
         <v>159</v>
       </c>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="41"/>
-    </row>
-    <row r="24" spans="2:10" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="62"/>
-      <c r="C24" s="63"/>
-      <c r="D24" s="63"/>
-      <c r="E24" s="63"/>
-      <c r="F24" s="56"/>
-      <c r="G24" s="38" t="s">
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="37"/>
+    </row>
+    <row r="23" spans="2:10" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B23" s="60"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="79"/>
+      <c r="G23" s="45" t="s">
         <v>160</v>
       </c>
-      <c r="H24" s="63"/>
-      <c r="I24" s="63"/>
-      <c r="J24" s="64"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="61"/>
+    </row>
+    <row r="24" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B24" s="51"/>
+      <c r="C24" s="52"/>
+      <c r="D24" s="52" t="s">
+        <v>161</v>
+      </c>
+      <c r="E24" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="F24" s="53" t="s">
+        <v>87</v>
+      </c>
+      <c r="G24" s="52"/>
+      <c r="H24" s="52"/>
+      <c r="I24" s="52" t="s">
+        <v>161</v>
+      </c>
+      <c r="J24" s="76" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="25" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="94"/>
-      <c r="C25" s="57"/>
-      <c r="D25" s="58" t="s">
+      <c r="B25" s="60"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41" t="s">
         <v>161</v>
       </c>
-      <c r="E25" s="92" t="s">
+      <c r="E25" s="39" t="s">
         <v>131</v>
       </c>
-      <c r="F25" s="59" t="s">
-        <v>87</v>
-      </c>
-      <c r="G25" s="58"/>
-      <c r="H25" s="58"/>
-      <c r="I25" s="58" t="s">
+      <c r="F25" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="G25" s="41"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="41" t="s">
         <v>161</v>
       </c>
-      <c r="J25" s="93" t="s">
+      <c r="J25" s="39" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="26" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="71"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45" t="s">
-        <v>161</v>
-      </c>
-      <c r="E26" s="43" t="s">
+    <row r="26" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B26" s="62"/>
+      <c r="C26" s="63"/>
+      <c r="D26" s="63"/>
+      <c r="E26" s="63"/>
+      <c r="F26" s="77" t="s">
+        <v>89</v>
+      </c>
+      <c r="G26" s="99" t="s">
+        <v>245</v>
+      </c>
+      <c r="H26" s="63"/>
+      <c r="I26" s="63"/>
+      <c r="J26" s="64"/>
+    </row>
+    <row r="27" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B27" s="15"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="78"/>
+      <c r="G27" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="18"/>
+    </row>
+    <row r="29" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="30" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="B30" s="83"/>
+      <c r="C30" s="84"/>
+      <c r="D30" s="84"/>
+      <c r="E30" s="84"/>
+      <c r="F30" s="84" t="s">
+        <v>122</v>
+      </c>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84"/>
+      <c r="I30" s="84"/>
+      <c r="J30" s="87"/>
+    </row>
+    <row r="31" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="B31" s="88" t="s">
+        <v>123</v>
+      </c>
+      <c r="C31" s="85"/>
+      <c r="D31" s="85"/>
+      <c r="E31" s="85"/>
+      <c r="F31" s="85"/>
+      <c r="G31" s="85" t="s">
+        <v>124</v>
+      </c>
+      <c r="H31" s="85"/>
+      <c r="I31" s="85"/>
+      <c r="J31" s="89"/>
+    </row>
+    <row r="32" spans="2:10" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B32" s="66" t="s">
+        <v>125</v>
+      </c>
+      <c r="C32" s="67" t="s">
+        <v>127</v>
+      </c>
+      <c r="D32" s="67" t="s">
+        <v>126</v>
+      </c>
+      <c r="E32" s="67" t="s">
+        <v>164</v>
+      </c>
+      <c r="F32" s="86"/>
+      <c r="G32" s="67" t="s">
+        <v>125</v>
+      </c>
+      <c r="H32" s="67" t="s">
+        <v>127</v>
+      </c>
+      <c r="I32" s="67" t="s">
+        <v>126</v>
+      </c>
+      <c r="J32" s="68" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="B33" s="35" t="s">
+        <v>193</v>
+      </c>
+      <c r="C33" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="D33" s="36" t="s">
+        <v>194</v>
+      </c>
+      <c r="E33" s="36" t="s">
+        <v>195</v>
+      </c>
+      <c r="F33" s="77" t="s">
+        <v>90</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="H33" s="24" t="s">
+        <v>199</v>
+      </c>
+      <c r="I33" s="104" t="s">
+        <v>202</v>
+      </c>
+      <c r="J33" s="105" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B34" s="13"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="79"/>
+      <c r="G34" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="I34" s="106" t="s">
+        <v>202</v>
+      </c>
+      <c r="J34" s="107" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B35" s="15"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="78"/>
+      <c r="G35" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="H35" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="I35" s="108" t="s">
+        <v>203</v>
+      </c>
+      <c r="J35" s="109" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B36" s="59" t="s">
+        <v>206</v>
+      </c>
+      <c r="C36" s="52" t="s">
+        <v>207</v>
+      </c>
+      <c r="D36" s="95" t="s">
+        <v>208</v>
+      </c>
+      <c r="E36" s="95" t="s">
+        <v>209</v>
+      </c>
+      <c r="F36" s="53" t="s">
+        <v>91</v>
+      </c>
+      <c r="G36" s="52"/>
+      <c r="H36" s="52"/>
+      <c r="I36" s="52"/>
+      <c r="J36" s="55"/>
+    </row>
+    <row r="37" spans="2:10" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B37" s="59" t="s">
+        <v>210</v>
+      </c>
+      <c r="C37" s="52" t="s">
+        <v>212</v>
+      </c>
+      <c r="D37" s="110" t="s">
+        <v>211</v>
+      </c>
+      <c r="E37" s="95" t="s">
+        <v>209</v>
+      </c>
+      <c r="F37" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="G37" s="52"/>
+      <c r="H37" s="52"/>
+      <c r="I37" s="52"/>
+      <c r="J37" s="55"/>
+    </row>
+    <row r="38" spans="2:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B38" s="51"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="53" t="s">
+        <v>93</v>
+      </c>
+      <c r="G38" s="52" t="s">
+        <v>213</v>
+      </c>
+      <c r="H38" s="52" t="s">
+        <v>214</v>
+      </c>
+      <c r="I38" s="110" t="s">
+        <v>215</v>
+      </c>
+      <c r="J38" s="111" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B39" s="72"/>
+      <c r="C39" s="73"/>
+      <c r="D39" s="73"/>
+      <c r="E39" s="65" t="s">
+        <v>162</v>
+      </c>
+      <c r="F39" s="74" t="s">
+        <v>94</v>
+      </c>
+      <c r="G39" s="73"/>
+      <c r="H39" s="73"/>
+      <c r="I39" s="73"/>
+      <c r="J39" s="65" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B40" s="51"/>
+      <c r="C40" s="52"/>
+      <c r="D40" s="52"/>
+      <c r="E40" s="75" t="s">
         <v>131</v>
       </c>
-      <c r="F26" s="44" t="s">
-        <v>88</v>
-      </c>
-      <c r="G26" s="45"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="45" t="s">
-        <v>161</v>
-      </c>
-      <c r="J26" s="43" t="s">
+      <c r="F40" s="53" t="s">
+        <v>95</v>
+      </c>
+      <c r="G40" s="52"/>
+      <c r="H40" s="52"/>
+      <c r="I40" s="52"/>
+      <c r="J40" s="76" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B27" s="71"/>
-      <c r="C27" s="72"/>
-      <c r="D27" s="72"/>
-      <c r="E27" s="72"/>
-      <c r="F27" s="55" t="s">
-        <v>89</v>
-      </c>
-      <c r="G27" s="72"/>
-      <c r="H27" s="72"/>
-      <c r="I27" s="72"/>
-      <c r="J27" s="73"/>
-    </row>
-    <row r="28" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="15"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="18"/>
-    </row>
-    <row r="30" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="31" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="B31" s="75"/>
-      <c r="C31" s="76"/>
-      <c r="D31" s="76"/>
-      <c r="E31" s="76"/>
-      <c r="F31" s="76" t="s">
+    <row r="41" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B41" s="51"/>
+      <c r="C41" s="52"/>
+      <c r="D41" s="52"/>
+      <c r="E41" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="F41" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="G41" s="52"/>
+      <c r="H41" s="52"/>
+      <c r="I41" s="52"/>
+      <c r="J41" s="76" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="44" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="B44" s="83"/>
+      <c r="C44" s="84"/>
+      <c r="D44" s="84"/>
+      <c r="E44" s="84"/>
+      <c r="F44" s="84" t="s">
         <v>122</v>
       </c>
-      <c r="G31" s="76"/>
-      <c r="H31" s="76"/>
-      <c r="I31" s="76"/>
-      <c r="J31" s="77"/>
-    </row>
-    <row r="32" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="B32" s="78" t="s">
+      <c r="G44" s="84"/>
+      <c r="H44" s="84"/>
+      <c r="I44" s="84"/>
+      <c r="J44" s="87"/>
+    </row>
+    <row r="45" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="B45" s="88" t="s">
         <v>123</v>
       </c>
-      <c r="C32" s="79"/>
-      <c r="D32" s="79"/>
-      <c r="E32" s="79"/>
-      <c r="F32" s="79"/>
-      <c r="G32" s="79" t="s">
+      <c r="C45" s="85"/>
+      <c r="D45" s="85"/>
+      <c r="E45" s="85"/>
+      <c r="F45" s="85"/>
+      <c r="G45" s="85" t="s">
         <v>124</v>
       </c>
-      <c r="H32" s="79"/>
-      <c r="I32" s="79"/>
-      <c r="J32" s="80"/>
-    </row>
-    <row r="33" spans="2:10" ht="19" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="81" t="s">
+      <c r="H45" s="85"/>
+      <c r="I45" s="85"/>
+      <c r="J45" s="89"/>
+    </row>
+    <row r="46" spans="2:10" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B46" s="66" t="s">
         <v>125</v>
       </c>
-      <c r="C33" s="82" t="s">
+      <c r="C46" s="67" t="s">
         <v>127</v>
       </c>
-      <c r="D33" s="82" t="s">
+      <c r="D46" s="67" t="s">
         <v>126</v>
       </c>
-      <c r="E33" s="82" t="s">
-        <v>164</v>
-      </c>
-      <c r="F33" s="83"/>
-      <c r="G33" s="82" t="s">
+      <c r="E46" s="67" t="s">
+        <v>165</v>
+      </c>
+      <c r="F46" s="86"/>
+      <c r="G46" s="67" t="s">
         <v>125</v>
       </c>
-      <c r="H33" s="82" t="s">
+      <c r="H46" s="67" t="s">
         <v>127</v>
       </c>
-      <c r="I33" s="82" t="s">
+      <c r="I46" s="67" t="s">
         <v>126</v>
       </c>
-      <c r="J33" s="84" t="s">
+      <c r="J46" s="68" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B34" s="25"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="55" t="s">
-        <v>90</v>
-      </c>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="41"/>
-    </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B35" s="13"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="14"/>
-    </row>
-    <row r="36" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="15"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="56"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="16"/>
-      <c r="I36" s="16"/>
-      <c r="J36" s="18"/>
-    </row>
-    <row r="37" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="57"/>
-      <c r="C37" s="58"/>
-      <c r="D37" s="58"/>
-      <c r="E37" s="58"/>
-      <c r="F37" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="G37" s="58"/>
-      <c r="H37" s="58"/>
-      <c r="I37" s="58"/>
-      <c r="J37" s="61"/>
-    </row>
-    <row r="38" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="57"/>
-      <c r="C38" s="58"/>
-      <c r="D38" s="58"/>
-      <c r="E38" s="58"/>
-      <c r="F38" s="59" t="s">
-        <v>92</v>
-      </c>
-      <c r="G38" s="58"/>
-      <c r="H38" s="58"/>
-      <c r="I38" s="58"/>
-      <c r="J38" s="61"/>
-    </row>
-    <row r="39" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B39" s="57"/>
-      <c r="C39" s="58"/>
-      <c r="D39" s="58"/>
-      <c r="E39" s="58"/>
-      <c r="F39" s="59" t="s">
-        <v>93</v>
-      </c>
-      <c r="G39" s="58"/>
-      <c r="H39" s="58"/>
-      <c r="I39" s="58"/>
-      <c r="J39" s="61"/>
-    </row>
-    <row r="40" spans="2:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="89"/>
-      <c r="C40" s="90"/>
-      <c r="D40" s="90"/>
-      <c r="E40" s="74" t="s">
-        <v>162</v>
-      </c>
-      <c r="F40" s="91" t="s">
-        <v>94</v>
-      </c>
-      <c r="G40" s="90"/>
-      <c r="H40" s="90"/>
-      <c r="I40" s="90"/>
-      <c r="J40" s="74" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="41" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="57"/>
-      <c r="C41" s="58"/>
-      <c r="D41" s="58"/>
-      <c r="E41" s="92" t="s">
+    <row r="47" spans="2:10" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B47" s="59" t="s">
+        <v>166</v>
+      </c>
+      <c r="C47" s="52" t="s">
+        <v>174</v>
+      </c>
+      <c r="D47" s="91" t="s">
+        <v>175</v>
+      </c>
+      <c r="E47" s="92" t="s">
+        <v>176</v>
+      </c>
+      <c r="F47" s="53" t="s">
+        <v>97</v>
+      </c>
+      <c r="G47" s="52"/>
+      <c r="H47" s="52"/>
+      <c r="I47" s="52"/>
+      <c r="J47" s="55"/>
+    </row>
+    <row r="48" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B48" s="72"/>
+      <c r="C48" s="73"/>
+      <c r="D48" s="73"/>
+      <c r="E48" s="73" t="s">
+        <v>163</v>
+      </c>
+      <c r="F48" s="74" t="s">
+        <v>98</v>
+      </c>
+      <c r="G48" s="73"/>
+      <c r="H48" s="73"/>
+      <c r="I48" s="73"/>
+      <c r="J48" s="73" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B49" s="51" t="s">
+        <v>167</v>
+      </c>
+      <c r="C49" s="52" t="s">
+        <v>178</v>
+      </c>
+      <c r="D49" s="94" t="s">
+        <v>177</v>
+      </c>
+      <c r="E49" s="95" t="s">
+        <v>179</v>
+      </c>
+      <c r="F49" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="G49" s="52"/>
+      <c r="H49" s="52"/>
+      <c r="I49" s="52"/>
+      <c r="J49" s="55"/>
+    </row>
+    <row r="50" spans="2:10" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B50" s="60" t="s">
+        <v>168</v>
+      </c>
+      <c r="C50" s="41" t="s">
+        <v>129</v>
+      </c>
+      <c r="D50" s="96" t="s">
+        <v>180</v>
+      </c>
+      <c r="E50" s="41"/>
+      <c r="F50" s="40" t="s">
+        <v>100</v>
+      </c>
+      <c r="G50" s="41" t="s">
+        <v>169</v>
+      </c>
+      <c r="H50" s="41" t="s">
+        <v>152</v>
+      </c>
+      <c r="I50" s="97" t="s">
+        <v>181</v>
+      </c>
+      <c r="J50" s="42" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B51" s="51" t="s">
+        <v>171</v>
+      </c>
+      <c r="C51" s="52" t="s">
+        <v>183</v>
+      </c>
+      <c r="D51" s="93" t="s">
+        <v>186</v>
+      </c>
+      <c r="E51" s="93" t="s">
+        <v>187</v>
+      </c>
+      <c r="F51" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="G51" s="54" t="s">
+        <v>170</v>
+      </c>
+      <c r="H51" s="54" t="s">
+        <v>156</v>
+      </c>
+      <c r="I51" s="91" t="s">
+        <v>184</v>
+      </c>
+      <c r="J51" s="98" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B52" s="60"/>
+      <c r="C52" s="41"/>
+      <c r="D52" s="41"/>
+      <c r="E52" s="39" t="s">
         <v>131</v>
       </c>
-      <c r="F41" s="59" t="s">
-        <v>95</v>
-      </c>
-      <c r="G41" s="58"/>
-      <c r="H41" s="58"/>
-      <c r="I41" s="58"/>
-      <c r="J41" s="93" t="s">
+      <c r="F52" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="G52" s="41"/>
+      <c r="H52" s="41"/>
+      <c r="I52" s="41"/>
+      <c r="J52" s="42" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="42" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="57"/>
-      <c r="C42" s="58"/>
-      <c r="D42" s="58"/>
-      <c r="E42" s="92" t="s">
+    <row r="53" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B53" s="51"/>
+      <c r="C53" s="52"/>
+      <c r="D53" s="52"/>
+      <c r="E53" s="75" t="s">
         <v>131</v>
       </c>
-      <c r="F42" s="59" t="s">
-        <v>96</v>
-      </c>
-      <c r="G42" s="58"/>
-      <c r="H42" s="58"/>
-      <c r="I42" s="58"/>
-      <c r="J42" s="93" t="s">
+      <c r="F53" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="G53" s="52"/>
+      <c r="H53" s="52"/>
+      <c r="I53" s="52"/>
+      <c r="J53" s="76" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="44" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="45" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="B45" s="75"/>
-      <c r="C45" s="76"/>
-      <c r="D45" s="76"/>
-      <c r="E45" s="76"/>
-      <c r="F45" s="76" t="s">
-        <v>122</v>
-      </c>
-      <c r="G45" s="76"/>
-      <c r="H45" s="76"/>
-      <c r="I45" s="76"/>
-      <c r="J45" s="77"/>
-    </row>
-    <row r="46" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="B46" s="78" t="s">
-        <v>123</v>
-      </c>
-      <c r="C46" s="79"/>
-      <c r="D46" s="79"/>
-      <c r="E46" s="79"/>
-      <c r="F46" s="79"/>
-      <c r="G46" s="79" t="s">
-        <v>124</v>
-      </c>
-      <c r="H46" s="79"/>
-      <c r="I46" s="79"/>
-      <c r="J46" s="80"/>
-    </row>
-    <row r="47" spans="2:10" ht="19" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B47" s="81" t="s">
-        <v>125</v>
-      </c>
-      <c r="C47" s="82" t="s">
-        <v>127</v>
-      </c>
-      <c r="D47" s="82" t="s">
-        <v>126</v>
-      </c>
-      <c r="E47" s="82" t="s">
-        <v>165</v>
-      </c>
-      <c r="F47" s="83"/>
-      <c r="G47" s="82" t="s">
-        <v>125</v>
-      </c>
-      <c r="H47" s="82" t="s">
-        <v>127</v>
-      </c>
-      <c r="I47" s="82" t="s">
-        <v>126</v>
-      </c>
-      <c r="J47" s="84" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="48" spans="2:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="68" t="s">
-        <v>166</v>
-      </c>
-      <c r="C48" s="58"/>
-      <c r="D48" s="58"/>
-      <c r="E48" s="58"/>
-      <c r="F48" s="59" t="s">
-        <v>97</v>
-      </c>
-      <c r="G48" s="58"/>
-      <c r="H48" s="58"/>
-      <c r="I48" s="58"/>
-      <c r="J48" s="61"/>
-    </row>
-    <row r="49" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B49" s="89"/>
-      <c r="C49" s="90"/>
-      <c r="D49" s="90"/>
-      <c r="E49" s="90" t="s">
-        <v>163</v>
-      </c>
-      <c r="F49" s="91" t="s">
-        <v>98</v>
-      </c>
-      <c r="G49" s="90"/>
-      <c r="H49" s="90"/>
-      <c r="I49" s="90"/>
-      <c r="J49" s="90" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="50" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="57" t="s">
-        <v>167</v>
-      </c>
-      <c r="C50" s="58"/>
-      <c r="D50" s="58"/>
-      <c r="E50" s="58"/>
-      <c r="F50" s="59" t="s">
-        <v>99</v>
-      </c>
-      <c r="G50" s="58"/>
-      <c r="H50" s="58"/>
-      <c r="I50" s="58"/>
-      <c r="J50" s="61"/>
-    </row>
-    <row r="51" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B51" s="69" t="s">
-        <v>168</v>
-      </c>
-      <c r="C51" s="45"/>
-      <c r="D51" s="45"/>
-      <c r="E51" s="45"/>
-      <c r="F51" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="G51" s="45" t="s">
-        <v>169</v>
-      </c>
-      <c r="H51" s="45"/>
-      <c r="I51" s="45"/>
-      <c r="J51" s="70"/>
-    </row>
-    <row r="52" spans="2:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="B52" s="25"/>
-      <c r="C52" s="26"/>
-      <c r="D52" s="26"/>
-      <c r="E52" s="26"/>
-      <c r="F52" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="G52" s="37" t="s">
-        <v>170</v>
-      </c>
-      <c r="H52" s="26"/>
-      <c r="I52" s="26"/>
-      <c r="J52" s="41"/>
-    </row>
-    <row r="53" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B53" s="15"/>
-      <c r="C53" s="16"/>
-      <c r="D53" s="16"/>
-      <c r="E53" s="16"/>
-      <c r="F53" s="56"/>
-      <c r="G53" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="H53" s="16"/>
-      <c r="I53" s="16"/>
-      <c r="J53" s="18"/>
-    </row>
-    <row r="54" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="69"/>
-      <c r="C54" s="45"/>
-      <c r="D54" s="45"/>
-      <c r="E54" s="43" t="s">
-        <v>131</v>
-      </c>
-      <c r="F54" s="44" t="s">
-        <v>102</v>
-      </c>
-      <c r="G54" s="45"/>
-      <c r="H54" s="45"/>
-      <c r="I54" s="45"/>
-      <c r="J54" s="46" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="55" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B55" s="57"/>
-      <c r="C55" s="58"/>
-      <c r="D55" s="58"/>
-      <c r="E55" s="92" t="s">
-        <v>131</v>
-      </c>
-      <c r="F55" s="59" t="s">
-        <v>103</v>
-      </c>
-      <c r="G55" s="58"/>
-      <c r="H55" s="58"/>
-      <c r="I55" s="58"/>
-      <c r="J55" s="93" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B56" s="71"/>
-      <c r="C56" s="72"/>
-      <c r="D56" s="72"/>
-      <c r="E56" s="72"/>
-      <c r="F56" s="55" t="s">
+    <row r="54" spans="2:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="B54" s="62"/>
+      <c r="C54" s="63"/>
+      <c r="D54" s="63"/>
+      <c r="E54" s="63"/>
+      <c r="F54" s="77" t="s">
         <v>104</v>
       </c>
-      <c r="G56" s="26" t="s">
+      <c r="G54" s="24" t="s">
         <v>172</v>
       </c>
-      <c r="H56" s="72"/>
-      <c r="I56" s="72"/>
-      <c r="J56" s="73"/>
-    </row>
-    <row r="57" spans="2:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B57" s="15"/>
-      <c r="C57" s="16"/>
-      <c r="D57" s="16"/>
-      <c r="E57" s="16"/>
-      <c r="F57" s="56"/>
-      <c r="G57" s="38" t="s">
+      <c r="H54" s="63" t="s">
+        <v>137</v>
+      </c>
+      <c r="I54" s="100" t="s">
+        <v>189</v>
+      </c>
+      <c r="J54" s="101" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B55" s="15"/>
+      <c r="C55" s="16"/>
+      <c r="D55" s="16"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="78"/>
+      <c r="G55" s="34" t="s">
         <v>173</v>
       </c>
-      <c r="H57" s="16"/>
-      <c r="I57" s="16"/>
-      <c r="J57" s="18"/>
+      <c r="H55" s="34" t="s">
+        <v>192</v>
+      </c>
+      <c r="I55" s="102" t="s">
+        <v>190</v>
+      </c>
+      <c r="J55" s="103" t="s">
+        <v>191</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="F27:F28"/>
-    <mergeCell ref="F34:F36"/>
-    <mergeCell ref="F52:F53"/>
-    <mergeCell ref="F56:F57"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="F9:F11"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="F13:F20"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="F31:F33"/>
-    <mergeCell ref="G31:J31"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="G32:J32"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="F45:F47"/>
-    <mergeCell ref="G45:J45"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="G46:J46"/>
+  <mergeCells count="23">
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="G3:J3"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="G2:J2"/>
     <mergeCell ref="F2:F4"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="F44:F46"/>
+    <mergeCell ref="G44:J44"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="G45:J45"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="F30:F32"/>
+    <mergeCell ref="G30:J30"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="G31:J31"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="F33:F35"/>
+    <mergeCell ref="F54:F55"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="F9:F11"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="F13:F19"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="D49" r:id="rId1" xr:uid="{1BDCDD1D-0819-496A-809D-C70FDD4A1FD8}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data/Suivi_Démarche_questionnaires_Janvier2026.xlsx
+++ b/Data/Suivi_Démarche_questionnaires_Janvier2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutroncj\Documents\Outils\FairCarboN_datas\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02E5E763-E7C5-44DC-89D2-5F6E99C0ADEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{449889A7-9703-44D3-8439-6F132BFBAAB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="267">
   <si>
     <t>1.2 Incertitudes</t>
   </si>
@@ -836,6 +836,69 @@
   </si>
   <si>
     <t>AGENT FORESTIER</t>
+  </si>
+  <si>
+    <t>Modele MARKLIT? DEV INDIVIDUEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MODULE  </t>
+  </si>
+  <si>
+    <t>Ne sait pas où sont stockées? Notice?</t>
+  </si>
+  <si>
+    <t>Méthodes MARL
+forge de F Michel</t>
+  </si>
+  <si>
+    <t>Réponses partielles</t>
+  </si>
+  <si>
+    <t>Aucun doc, aucune source</t>
+  </si>
+  <si>
+    <t>Forge MIA
+article de recherche</t>
+  </si>
+  <si>
+    <t>SCRIPT COLLECTIF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>DATA ENQUETE</t>
+  </si>
+  <si>
+    <t>Dossier Sygade</t>
+  </si>
+  <si>
+    <t>peu d'infos, mais data sensibles</t>
+  </si>
+  <si>
+    <t>MODELE</t>
+  </si>
+  <si>
+    <t>Description très succinte</t>
+  </si>
+  <si>
+    <t>modele Sysmetha-matlab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peu de chose
+usage privé? </t>
+  </si>
+  <si>
+    <t>modèle Matlab R2021A?</t>
+  </si>
+  <si>
+    <t>Modèle Matlab R2021A?</t>
+  </si>
+  <si>
+    <t>from heuristics, existing knowledges, no docs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peu d'infos </t>
   </si>
 </sst>
 </file>
@@ -1327,7 +1390,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1368,9 +1431,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1380,9 +1440,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1419,9 +1476,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1437,9 +1491,6 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1509,18 +1560,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1557,6 +1602,102 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="22" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1575,125 +1716,66 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="22" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -2867,171 +2949,171 @@
   <sheetData>
     <row r="1" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84" t="s">
+      <c r="B2" s="98"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99" t="s">
         <v>122</v>
       </c>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="87"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="100"/>
     </row>
     <row r="3" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="B3" s="88" t="s">
+      <c r="B3" s="95" t="s">
         <v>123</v>
       </c>
-      <c r="C3" s="85"/>
-      <c r="D3" s="85"/>
-      <c r="E3" s="85"/>
-      <c r="F3" s="85"/>
-      <c r="G3" s="85" t="s">
+      <c r="C3" s="96"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="96" t="s">
         <v>124</v>
       </c>
-      <c r="H3" s="85"/>
-      <c r="I3" s="85"/>
-      <c r="J3" s="89"/>
+      <c r="H3" s="96"/>
+      <c r="I3" s="96"/>
+      <c r="J3" s="97"/>
     </row>
     <row r="4" spans="2:10" ht="19" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="69" t="s">
+      <c r="B4" s="63" t="s">
         <v>125</v>
       </c>
-      <c r="C4" s="70" t="s">
+      <c r="C4" s="64" t="s">
         <v>127</v>
       </c>
-      <c r="D4" s="70" t="s">
+      <c r="D4" s="64" t="s">
         <v>126</v>
       </c>
-      <c r="E4" s="70" t="s">
+      <c r="E4" s="64" t="s">
         <v>164</v>
       </c>
-      <c r="F4" s="90"/>
-      <c r="G4" s="70" t="s">
+      <c r="F4" s="101"/>
+      <c r="G4" s="64" t="s">
         <v>125</v>
       </c>
-      <c r="H4" s="70" t="s">
+      <c r="H4" s="64" t="s">
         <v>127</v>
       </c>
-      <c r="I4" s="70" t="s">
+      <c r="I4" s="64" t="s">
         <v>126</v>
       </c>
-      <c r="J4" s="71" t="s">
+      <c r="J4" s="65" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B5" s="23"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="80" t="s">
+      <c r="B5" s="21"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="106" t="s">
         <v>79</v>
       </c>
-      <c r="G5" s="25" t="s">
+      <c r="G5" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="H5" s="25" t="s">
+      <c r="H5" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="I5" s="26" t="s">
+      <c r="I5" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="J5" s="27" t="s">
+      <c r="J5" s="25" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="6" spans="2:10" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="15"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="28" t="s">
+      <c r="B6" s="14"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="107"/>
+      <c r="G6" s="26" t="s">
         <v>132</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="I6" s="29" t="s">
+      <c r="I6" s="27" t="s">
         <v>135</v>
       </c>
-      <c r="J6" s="30" t="s">
+      <c r="J6" s="28" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="7" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B7" s="32"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="80" t="s">
+      <c r="B7" s="29"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="106" t="s">
         <v>80</v>
       </c>
-      <c r="G7" s="33" t="s">
+      <c r="G7" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="H7" s="25" t="s">
+      <c r="H7" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="I7" s="26" t="s">
+      <c r="I7" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="J7" s="27" t="s">
+      <c r="J7" s="25" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="8" spans="2:10" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="43"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="82"/>
-      <c r="G8" s="45" t="s">
+      <c r="B8" s="39"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="108"/>
+      <c r="G8" s="41" t="s">
         <v>138</v>
       </c>
-      <c r="H8" s="46" t="s">
+      <c r="H8" s="42" t="s">
         <v>140</v>
       </c>
-      <c r="I8" s="47" t="s">
+      <c r="I8" s="43" t="s">
         <v>141</v>
       </c>
-      <c r="J8" s="48" t="s">
+      <c r="J8" s="44" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="9" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B9" s="35" t="s">
+      <c r="B9" s="32" t="s">
         <v>143</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="33" t="s">
         <v>145</v>
       </c>
-      <c r="E9" s="36" t="s">
+      <c r="E9" s="33" t="s">
         <v>146</v>
       </c>
-      <c r="F9" s="77" t="s">
+      <c r="F9" s="103" t="s">
         <v>81</v>
       </c>
-      <c r="G9" s="33" t="s">
+      <c r="G9" s="30" t="s">
         <v>149</v>
       </c>
-      <c r="H9" s="24" t="s">
+      <c r="H9" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="I9" s="26" t="s">
+      <c r="I9" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="J9" s="27" t="s">
+      <c r="J9" s="25" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="10" spans="2:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="18" t="s">
         <v>144</v>
       </c>
       <c r="C10" s="6" t="s">
@@ -3043,7 +3125,7 @@
       <c r="E10" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F10" s="79"/>
+      <c r="F10" s="105"/>
       <c r="G10" s="6" t="s">
         <v>150</v>
       </c>
@@ -3053,421 +3135,471 @@
       <c r="I10" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="J10" s="19" t="s">
+      <c r="J10" s="17" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="11" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="38"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="16" t="s">
+      <c r="B11" s="34"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="H11" s="16" t="s">
+      <c r="H11" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="I11" s="49" t="s">
+      <c r="I11" s="45" t="s">
         <v>154</v>
       </c>
-      <c r="J11" s="50" t="s">
+      <c r="J11" s="46" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="12" spans="2:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="51"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="53" t="s">
+      <c r="B12" s="47"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="49" t="s">
         <v>82</v>
       </c>
-      <c r="G12" s="54" t="s">
+      <c r="G12" s="50" t="s">
         <v>155</v>
       </c>
-      <c r="H12" s="54" t="s">
+      <c r="H12" s="50" t="s">
         <v>156</v>
       </c>
-      <c r="I12" s="95" t="s">
+      <c r="I12" s="75" t="s">
         <v>218</v>
       </c>
-      <c r="J12" s="111" t="s">
+      <c r="J12" s="85" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="13" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B13" s="35" t="s">
+      <c r="B13" s="32" t="s">
         <v>219</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="22" t="s">
         <v>201</v>
       </c>
-      <c r="D13" s="113" t="s">
+      <c r="D13" s="24" t="s">
         <v>224</v>
       </c>
-      <c r="E13" s="113" t="s">
+      <c r="E13" s="24" t="s">
         <v>223</v>
       </c>
-      <c r="F13" s="77" t="s">
+      <c r="F13" s="103" t="s">
         <v>83</v>
       </c>
-      <c r="G13" s="33" t="s">
+      <c r="G13" s="30" t="s">
         <v>231</v>
       </c>
-      <c r="H13" s="33" t="s">
+      <c r="H13" s="30" t="s">
         <v>192</v>
       </c>
-      <c r="I13" s="104" t="s">
+      <c r="I13" s="83" t="s">
         <v>233</v>
       </c>
-      <c r="J13" s="122" t="s">
+      <c r="J13" s="94" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="14" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="20" t="s">
         <v>201</v>
       </c>
-      <c r="D14" s="114" t="s">
+      <c r="D14" s="88" t="s">
         <v>227</v>
       </c>
-      <c r="E14" s="115" t="s">
+      <c r="E14" s="89" t="s">
         <v>223</v>
       </c>
-      <c r="F14" s="79"/>
+      <c r="F14" s="105"/>
       <c r="G14" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="H14" s="22" t="s">
+      <c r="H14" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="I14" s="116" t="s">
+      <c r="I14" s="89" t="s">
         <v>237</v>
       </c>
-      <c r="J14" s="119" t="s">
+      <c r="J14" s="93" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="15" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="D15" s="116" t="s">
+      <c r="D15" s="90" t="s">
         <v>226</v>
       </c>
-      <c r="E15" s="117" t="s">
+      <c r="E15" s="91" t="s">
         <v>225</v>
       </c>
-      <c r="F15" s="79"/>
-      <c r="G15" s="112" t="s">
+      <c r="F15" s="105"/>
+      <c r="G15" s="86" t="s">
         <v>238</v>
       </c>
-      <c r="H15" s="22" t="s">
+      <c r="H15" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="I15" s="115" t="s">
+      <c r="I15" s="89" t="s">
         <v>239</v>
       </c>
-      <c r="J15" s="121"/>
+      <c r="J15" s="93"/>
     </row>
     <row r="16" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="D16" s="114" t="s">
+      <c r="D16" s="123" t="s">
         <v>229</v>
       </c>
-      <c r="E16" s="115" t="s">
+      <c r="E16" s="120" t="s">
         <v>228</v>
       </c>
-      <c r="F16" s="79"/>
+      <c r="F16" s="105"/>
       <c r="G16" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="H16" s="22" t="s">
+      <c r="H16" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="I16" s="22"/>
-      <c r="J16" s="31"/>
+      <c r="I16" s="120" t="s">
+        <v>261</v>
+      </c>
+      <c r="J16" s="121" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="17" spans="2:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="B17" s="118" t="s">
+      <c r="B17" s="92" t="s">
         <v>230</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="D17" s="117" t="s">
+      <c r="D17" s="88" t="s">
         <v>235</v>
       </c>
-      <c r="E17" s="116" t="s">
+      <c r="E17" s="89" t="s">
         <v>236</v>
       </c>
-      <c r="F17" s="79"/>
+      <c r="F17" s="105"/>
       <c r="G17" s="6" t="s">
         <v>241</v>
       </c>
       <c r="H17" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="I17" s="120"/>
-      <c r="J17" s="123"/>
+      <c r="I17" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="J17" s="122" t="s">
+        <v>262</v>
+      </c>
     </row>
     <row r="18" spans="2:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="B18" s="21"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="79"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="105"/>
       <c r="G18" s="6" t="s">
         <v>242</v>
       </c>
       <c r="H18" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="I18" s="120"/>
-      <c r="J18" s="123"/>
+      <c r="I18" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="J18" s="122" t="s">
+        <v>262</v>
+      </c>
     </row>
     <row r="19" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B19" s="21"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="79"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="105"/>
       <c r="G19" s="6" t="s">
         <v>243</v>
       </c>
       <c r="H19" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="I19" s="10"/>
-      <c r="J19" s="14"/>
-    </row>
-    <row r="20" spans="2:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="56"/>
-      <c r="C20" s="57"/>
-      <c r="D20" s="57"/>
-      <c r="E20" s="65" t="s">
+      <c r="I19" s="124" t="s">
+        <v>265</v>
+      </c>
+      <c r="J19" s="125"/>
+    </row>
+    <row r="20" spans="2:10" ht="33.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B20" s="52"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="59" t="s">
         <v>162</v>
       </c>
-      <c r="F20" s="58" t="s">
+      <c r="F20" s="54" t="s">
         <v>84</v>
       </c>
-      <c r="G20" s="57"/>
-      <c r="H20" s="57"/>
-      <c r="I20" s="57"/>
-      <c r="J20" s="65" t="s">
+      <c r="G20" s="53"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="59" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="21" spans="2:10" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="59" t="s">
+      <c r="B21" s="55" t="s">
         <v>157</v>
       </c>
-      <c r="C21" s="52"/>
-      <c r="D21" s="52"/>
-      <c r="E21" s="52"/>
-      <c r="F21" s="53" t="s">
+      <c r="C21" s="48" t="s">
+        <v>174</v>
+      </c>
+      <c r="D21" s="118" t="s">
+        <v>252</v>
+      </c>
+      <c r="E21" s="69" t="s">
+        <v>255</v>
+      </c>
+      <c r="F21" s="49" t="s">
         <v>85</v>
       </c>
-      <c r="G21" s="52" t="s">
+      <c r="G21" s="48" t="s">
         <v>158</v>
       </c>
-      <c r="H21" s="52"/>
-      <c r="I21" s="52"/>
-      <c r="J21" s="55"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B22" s="23"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="77" t="s">
+      <c r="H21" s="48" t="s">
+        <v>254</v>
+      </c>
+      <c r="I21" s="113" t="s">
+        <v>253</v>
+      </c>
+      <c r="J21" s="119" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="B22" s="21"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="103" t="s">
         <v>86</v>
       </c>
-      <c r="G22" s="33" t="s">
+      <c r="G22" s="30" t="s">
         <v>159</v>
       </c>
-      <c r="H22" s="24"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="37"/>
+      <c r="H22" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="I22" s="109" t="s">
+        <v>247</v>
+      </c>
+      <c r="J22" s="110" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="23" spans="2:10" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="60"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="79"/>
-      <c r="G23" s="45" t="s">
+      <c r="B23" s="56"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="105"/>
+      <c r="G23" s="41" t="s">
         <v>160</v>
       </c>
-      <c r="H23" s="41"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="61"/>
+      <c r="H23" s="37" t="s">
+        <v>248</v>
+      </c>
+      <c r="I23" s="111" t="s">
+        <v>250</v>
+      </c>
+      <c r="J23" s="112" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="24" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="51"/>
-      <c r="C24" s="52"/>
-      <c r="D24" s="52" t="s">
+      <c r="B24" s="47"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="E24" s="75" t="s">
+      <c r="E24" s="69" t="s">
         <v>131</v>
       </c>
-      <c r="F24" s="53" t="s">
+      <c r="F24" s="49" t="s">
         <v>87</v>
       </c>
-      <c r="G24" s="52"/>
-      <c r="H24" s="52"/>
-      <c r="I24" s="52" t="s">
+      <c r="G24" s="48"/>
+      <c r="H24" s="48"/>
+      <c r="I24" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="J24" s="76" t="s">
+      <c r="J24" s="70" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="25" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="60"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="41" t="s">
+      <c r="B25" s="56"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37" t="s">
         <v>161</v>
       </c>
-      <c r="E25" s="39" t="s">
+      <c r="E25" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="F25" s="40" t="s">
+      <c r="F25" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="G25" s="41"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="41" t="s">
+      <c r="G25" s="37"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="37" t="s">
         <v>161</v>
       </c>
-      <c r="J25" s="39" t="s">
+      <c r="J25" s="35" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="26" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B26" s="62"/>
-      <c r="C26" s="63"/>
-      <c r="D26" s="63"/>
-      <c r="E26" s="63"/>
-      <c r="F26" s="77" t="s">
+      <c r="B26" s="57"/>
+      <c r="C26" s="58"/>
+      <c r="D26" s="58"/>
+      <c r="E26" s="58"/>
+      <c r="F26" s="103" t="s">
         <v>89</v>
       </c>
-      <c r="G26" s="99" t="s">
+      <c r="G26" s="78" t="s">
         <v>245</v>
       </c>
-      <c r="H26" s="63"/>
-      <c r="I26" s="63"/>
-      <c r="J26" s="64"/>
+      <c r="H26" s="58" t="s">
+        <v>256</v>
+      </c>
+      <c r="I26" s="114" t="s">
+        <v>257</v>
+      </c>
+      <c r="J26" s="115" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="27" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="15"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="78"/>
-      <c r="G27" s="16" t="s">
+      <c r="B27" s="14"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="104"/>
+      <c r="G27" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="18"/>
+      <c r="H27" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="I27" s="116" t="s">
+        <v>260</v>
+      </c>
+      <c r="J27" s="117" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="29" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="B30" s="83"/>
-      <c r="C30" s="84"/>
-      <c r="D30" s="84"/>
-      <c r="E30" s="84"/>
-      <c r="F30" s="84" t="s">
+      <c r="B30" s="98"/>
+      <c r="C30" s="99"/>
+      <c r="D30" s="99"/>
+      <c r="E30" s="99"/>
+      <c r="F30" s="99" t="s">
         <v>122</v>
       </c>
-      <c r="G30" s="84"/>
-      <c r="H30" s="84"/>
-      <c r="I30" s="84"/>
-      <c r="J30" s="87"/>
+      <c r="G30" s="99"/>
+      <c r="H30" s="99"/>
+      <c r="I30" s="99"/>
+      <c r="J30" s="100"/>
     </row>
     <row r="31" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="B31" s="88" t="s">
+      <c r="B31" s="95" t="s">
         <v>123</v>
       </c>
-      <c r="C31" s="85"/>
-      <c r="D31" s="85"/>
-      <c r="E31" s="85"/>
-      <c r="F31" s="85"/>
-      <c r="G31" s="85" t="s">
+      <c r="C31" s="96"/>
+      <c r="D31" s="96"/>
+      <c r="E31" s="96"/>
+      <c r="F31" s="96"/>
+      <c r="G31" s="96" t="s">
         <v>124</v>
       </c>
-      <c r="H31" s="85"/>
-      <c r="I31" s="85"/>
-      <c r="J31" s="89"/>
+      <c r="H31" s="96"/>
+      <c r="I31" s="96"/>
+      <c r="J31" s="97"/>
     </row>
     <row r="32" spans="2:10" ht="19" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="66" t="s">
+      <c r="B32" s="60" t="s">
         <v>125</v>
       </c>
-      <c r="C32" s="67" t="s">
+      <c r="C32" s="61" t="s">
         <v>127</v>
       </c>
-      <c r="D32" s="67" t="s">
+      <c r="D32" s="61" t="s">
         <v>126</v>
       </c>
-      <c r="E32" s="67" t="s">
+      <c r="E32" s="61" t="s">
         <v>164</v>
       </c>
-      <c r="F32" s="86"/>
-      <c r="G32" s="67" t="s">
+      <c r="F32" s="102"/>
+      <c r="G32" s="61" t="s">
         <v>125</v>
       </c>
-      <c r="H32" s="67" t="s">
+      <c r="H32" s="61" t="s">
         <v>127</v>
       </c>
-      <c r="I32" s="67" t="s">
+      <c r="I32" s="61" t="s">
         <v>126</v>
       </c>
-      <c r="J32" s="68" t="s">
+      <c r="J32" s="62" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="33" spans="2:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="B33" s="35" t="s">
+      <c r="B33" s="32" t="s">
         <v>193</v>
       </c>
-      <c r="C33" s="24" t="s">
+      <c r="C33" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="D33" s="36" t="s">
+      <c r="D33" s="33" t="s">
         <v>194</v>
       </c>
-      <c r="E33" s="36" t="s">
+      <c r="E33" s="33" t="s">
         <v>195</v>
       </c>
-      <c r="F33" s="77" t="s">
+      <c r="F33" s="103" t="s">
         <v>90</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="H33" s="24" t="s">
+      <c r="H33" s="22" t="s">
         <v>199</v>
       </c>
-      <c r="I33" s="104" t="s">
+      <c r="I33" s="87" t="s">
         <v>202</v>
       </c>
-      <c r="J33" s="105" t="s">
+      <c r="J33" s="110" t="s">
         <v>204</v>
       </c>
     </row>
@@ -3476,415 +3608,400 @@
       <c r="C34" s="10"/>
       <c r="D34" s="10"/>
       <c r="E34" s="10"/>
-      <c r="F34" s="79"/>
+      <c r="F34" s="105"/>
       <c r="G34" s="10" t="s">
         <v>197</v>
       </c>
       <c r="H34" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="I34" s="106" t="s">
+      <c r="I34" s="126" t="s">
         <v>202</v>
       </c>
-      <c r="J34" s="107" t="s">
+      <c r="J34" s="125" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="35" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="15"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="78"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="104"/>
       <c r="G35" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="H35" s="16" t="s">
+      <c r="H35" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="I35" s="108" t="s">
+      <c r="I35" s="127" t="s">
         <v>203</v>
       </c>
-      <c r="J35" s="109" t="s">
+      <c r="J35" s="128" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="36" spans="2:10" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="59" t="s">
+      <c r="B36" s="55" t="s">
         <v>206</v>
       </c>
-      <c r="C36" s="52" t="s">
+      <c r="C36" s="48" t="s">
         <v>207</v>
       </c>
-      <c r="D36" s="95" t="s">
+      <c r="D36" s="113" t="s">
         <v>208</v>
       </c>
-      <c r="E36" s="95" t="s">
+      <c r="E36" s="113" t="s">
         <v>209</v>
       </c>
-      <c r="F36" s="53" t="s">
+      <c r="F36" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="G36" s="52"/>
-      <c r="H36" s="52"/>
-      <c r="I36" s="52"/>
-      <c r="J36" s="55"/>
+      <c r="G36" s="48"/>
+      <c r="H36" s="48"/>
+      <c r="I36" s="48"/>
+      <c r="J36" s="51"/>
     </row>
     <row r="37" spans="2:10" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="59" t="s">
+      <c r="B37" s="55" t="s">
         <v>210</v>
       </c>
-      <c r="C37" s="52" t="s">
+      <c r="C37" s="48" t="s">
         <v>212</v>
       </c>
-      <c r="D37" s="110" t="s">
+      <c r="D37" s="84" t="s">
         <v>211</v>
       </c>
-      <c r="E37" s="95" t="s">
-        <v>209</v>
-      </c>
-      <c r="F37" s="53" t="s">
+      <c r="E37" s="75" t="s">
+        <v>266</v>
+      </c>
+      <c r="F37" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="G37" s="52"/>
-      <c r="H37" s="52"/>
-      <c r="I37" s="52"/>
-      <c r="J37" s="55"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="48"/>
+      <c r="J37" s="51"/>
     </row>
     <row r="38" spans="2:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="51"/>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="53" t="s">
+      <c r="B38" s="47"/>
+      <c r="C38" s="48"/>
+      <c r="D38" s="48"/>
+      <c r="E38" s="48"/>
+      <c r="F38" s="49" t="s">
         <v>93</v>
       </c>
-      <c r="G38" s="52" t="s">
+      <c r="G38" s="48" t="s">
         <v>213</v>
       </c>
-      <c r="H38" s="52" t="s">
+      <c r="H38" s="48" t="s">
         <v>214</v>
       </c>
-      <c r="I38" s="110" t="s">
+      <c r="I38" s="84" t="s">
         <v>215</v>
       </c>
-      <c r="J38" s="111" t="s">
+      <c r="J38" s="85" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="39" spans="2:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B39" s="72"/>
-      <c r="C39" s="73"/>
-      <c r="D39" s="73"/>
-      <c r="E39" s="65" t="s">
+      <c r="B39" s="66"/>
+      <c r="C39" s="67"/>
+      <c r="D39" s="67"/>
+      <c r="E39" s="59" t="s">
         <v>162</v>
       </c>
-      <c r="F39" s="74" t="s">
+      <c r="F39" s="68" t="s">
         <v>94</v>
       </c>
-      <c r="G39" s="73"/>
-      <c r="H39" s="73"/>
-      <c r="I39" s="73"/>
-      <c r="J39" s="65" t="s">
+      <c r="G39" s="67"/>
+      <c r="H39" s="67"/>
+      <c r="I39" s="67"/>
+      <c r="J39" s="59" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="40" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="51"/>
-      <c r="C40" s="52"/>
-      <c r="D40" s="52"/>
-      <c r="E40" s="75" t="s">
+      <c r="B40" s="47"/>
+      <c r="C40" s="48"/>
+      <c r="D40" s="48"/>
+      <c r="E40" s="69" t="s">
         <v>131</v>
       </c>
-      <c r="F40" s="53" t="s">
+      <c r="F40" s="49" t="s">
         <v>95</v>
       </c>
-      <c r="G40" s="52"/>
-      <c r="H40" s="52"/>
-      <c r="I40" s="52"/>
-      <c r="J40" s="76" t="s">
+      <c r="G40" s="48"/>
+      <c r="H40" s="48"/>
+      <c r="I40" s="48"/>
+      <c r="J40" s="70" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="41" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="51"/>
-      <c r="C41" s="52"/>
-      <c r="D41" s="52"/>
-      <c r="E41" s="75" t="s">
+      <c r="B41" s="47"/>
+      <c r="C41" s="48"/>
+      <c r="D41" s="48"/>
+      <c r="E41" s="69" t="s">
         <v>131</v>
       </c>
-      <c r="F41" s="53" t="s">
+      <c r="F41" s="49" t="s">
         <v>96</v>
       </c>
-      <c r="G41" s="52"/>
-      <c r="H41" s="52"/>
-      <c r="I41" s="52"/>
-      <c r="J41" s="76" t="s">
+      <c r="G41" s="48"/>
+      <c r="H41" s="48"/>
+      <c r="I41" s="48"/>
+      <c r="J41" s="70" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="43" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="44" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="B44" s="83"/>
-      <c r="C44" s="84"/>
-      <c r="D44" s="84"/>
-      <c r="E44" s="84"/>
-      <c r="F44" s="84" t="s">
+      <c r="B44" s="98"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
+      <c r="F44" s="99" t="s">
         <v>122</v>
       </c>
-      <c r="G44" s="84"/>
-      <c r="H44" s="84"/>
-      <c r="I44" s="84"/>
-      <c r="J44" s="87"/>
+      <c r="G44" s="99"/>
+      <c r="H44" s="99"/>
+      <c r="I44" s="99"/>
+      <c r="J44" s="100"/>
     </row>
     <row r="45" spans="2:10" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="B45" s="88" t="s">
+      <c r="B45" s="95" t="s">
         <v>123</v>
       </c>
-      <c r="C45" s="85"/>
-      <c r="D45" s="85"/>
-      <c r="E45" s="85"/>
-      <c r="F45" s="85"/>
-      <c r="G45" s="85" t="s">
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
+      <c r="F45" s="96"/>
+      <c r="G45" s="96" t="s">
         <v>124</v>
       </c>
-      <c r="H45" s="85"/>
-      <c r="I45" s="85"/>
-      <c r="J45" s="89"/>
+      <c r="H45" s="96"/>
+      <c r="I45" s="96"/>
+      <c r="J45" s="97"/>
     </row>
     <row r="46" spans="2:10" ht="19" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="66" t="s">
+      <c r="B46" s="60" t="s">
         <v>125</v>
       </c>
-      <c r="C46" s="67" t="s">
+      <c r="C46" s="61" t="s">
         <v>127</v>
       </c>
-      <c r="D46" s="67" t="s">
+      <c r="D46" s="61" t="s">
         <v>126</v>
       </c>
-      <c r="E46" s="67" t="s">
+      <c r="E46" s="61" t="s">
         <v>165</v>
       </c>
-      <c r="F46" s="86"/>
-      <c r="G46" s="67" t="s">
+      <c r="F46" s="102"/>
+      <c r="G46" s="61" t="s">
         <v>125</v>
       </c>
-      <c r="H46" s="67" t="s">
+      <c r="H46" s="61" t="s">
         <v>127</v>
       </c>
-      <c r="I46" s="67" t="s">
+      <c r="I46" s="61" t="s">
         <v>126</v>
       </c>
-      <c r="J46" s="68" t="s">
+      <c r="J46" s="62" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="47" spans="2:10" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B47" s="59" t="s">
+      <c r="B47" s="55" t="s">
         <v>166</v>
       </c>
-      <c r="C47" s="52" t="s">
+      <c r="C47" s="48" t="s">
         <v>174</v>
       </c>
-      <c r="D47" s="91" t="s">
+      <c r="D47" s="71" t="s">
         <v>175</v>
       </c>
-      <c r="E47" s="92" t="s">
+      <c r="E47" s="72" t="s">
         <v>176</v>
       </c>
-      <c r="F47" s="53" t="s">
+      <c r="F47" s="49" t="s">
         <v>97</v>
       </c>
-      <c r="G47" s="52"/>
-      <c r="H47" s="52"/>
-      <c r="I47" s="52"/>
-      <c r="J47" s="55"/>
+      <c r="G47" s="48"/>
+      <c r="H47" s="48"/>
+      <c r="I47" s="48"/>
+      <c r="J47" s="51"/>
     </row>
     <row r="48" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="72"/>
-      <c r="C48" s="73"/>
-      <c r="D48" s="73"/>
-      <c r="E48" s="73" t="s">
+      <c r="B48" s="66"/>
+      <c r="C48" s="67"/>
+      <c r="D48" s="67"/>
+      <c r="E48" s="67" t="s">
         <v>163</v>
       </c>
-      <c r="F48" s="74" t="s">
+      <c r="F48" s="68" t="s">
         <v>98</v>
       </c>
-      <c r="G48" s="73"/>
-      <c r="H48" s="73"/>
-      <c r="I48" s="73"/>
-      <c r="J48" s="73" t="s">
+      <c r="G48" s="67"/>
+      <c r="H48" s="67"/>
+      <c r="I48" s="67"/>
+      <c r="J48" s="67" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="49" spans="2:10" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B49" s="51" t="s">
+      <c r="B49" s="47" t="s">
         <v>167</v>
       </c>
-      <c r="C49" s="52" t="s">
+      <c r="C49" s="48" t="s">
         <v>178</v>
       </c>
-      <c r="D49" s="94" t="s">
+      <c r="D49" s="74" t="s">
         <v>177</v>
       </c>
-      <c r="E49" s="95" t="s">
+      <c r="E49" s="75" t="s">
         <v>179</v>
       </c>
-      <c r="F49" s="53" t="s">
+      <c r="F49" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="G49" s="52"/>
-      <c r="H49" s="52"/>
-      <c r="I49" s="52"/>
-      <c r="J49" s="55"/>
+      <c r="G49" s="48"/>
+      <c r="H49" s="48"/>
+      <c r="I49" s="48"/>
+      <c r="J49" s="51"/>
     </row>
     <row r="50" spans="2:10" ht="44" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="60" t="s">
+      <c r="B50" s="56" t="s">
         <v>168</v>
       </c>
-      <c r="C50" s="41" t="s">
+      <c r="C50" s="37" t="s">
         <v>129</v>
       </c>
-      <c r="D50" s="96" t="s">
+      <c r="D50" s="76" t="s">
         <v>180</v>
       </c>
-      <c r="E50" s="41"/>
-      <c r="F50" s="40" t="s">
+      <c r="E50" s="35"/>
+      <c r="F50" s="36" t="s">
         <v>100</v>
       </c>
-      <c r="G50" s="41" t="s">
+      <c r="G50" s="37" t="s">
         <v>169</v>
       </c>
-      <c r="H50" s="41" t="s">
+      <c r="H50" s="37" t="s">
         <v>152</v>
       </c>
-      <c r="I50" s="97" t="s">
+      <c r="I50" s="76" t="s">
         <v>181</v>
       </c>
-      <c r="J50" s="42" t="s">
+      <c r="J50" s="38" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="51" spans="2:10" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B51" s="51" t="s">
+      <c r="B51" s="47" t="s">
         <v>171</v>
       </c>
-      <c r="C51" s="52" t="s">
+      <c r="C51" s="48" t="s">
         <v>183</v>
       </c>
-      <c r="D51" s="93" t="s">
+      <c r="D51" s="73" t="s">
         <v>186</v>
       </c>
-      <c r="E51" s="93" t="s">
+      <c r="E51" s="73" t="s">
         <v>187</v>
       </c>
-      <c r="F51" s="53" t="s">
+      <c r="F51" s="49" t="s">
         <v>101</v>
       </c>
-      <c r="G51" s="54" t="s">
+      <c r="G51" s="50" t="s">
         <v>170</v>
       </c>
-      <c r="H51" s="54" t="s">
+      <c r="H51" s="50" t="s">
         <v>156</v>
       </c>
-      <c r="I51" s="91" t="s">
+      <c r="I51" s="71" t="s">
         <v>184</v>
       </c>
-      <c r="J51" s="98" t="s">
+      <c r="J51" s="77" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="52" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="60"/>
-      <c r="C52" s="41"/>
-      <c r="D52" s="41"/>
-      <c r="E52" s="39" t="s">
+      <c r="B52" s="56"/>
+      <c r="C52" s="37"/>
+      <c r="D52" s="37"/>
+      <c r="E52" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="F52" s="40" t="s">
+      <c r="F52" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="G52" s="41"/>
-      <c r="H52" s="41"/>
-      <c r="I52" s="41"/>
-      <c r="J52" s="42" t="s">
+      <c r="G52" s="37"/>
+      <c r="H52" s="37"/>
+      <c r="I52" s="37"/>
+      <c r="J52" s="38" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="53" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B53" s="51"/>
-      <c r="C53" s="52"/>
-      <c r="D53" s="52"/>
-      <c r="E53" s="75" t="s">
+      <c r="B53" s="47"/>
+      <c r="C53" s="48"/>
+      <c r="D53" s="48"/>
+      <c r="E53" s="69" t="s">
         <v>131</v>
       </c>
-      <c r="F53" s="53" t="s">
+      <c r="F53" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="G53" s="52"/>
-      <c r="H53" s="52"/>
-      <c r="I53" s="52"/>
-      <c r="J53" s="76" t="s">
+      <c r="G53" s="48"/>
+      <c r="H53" s="48"/>
+      <c r="I53" s="48"/>
+      <c r="J53" s="70" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="54" spans="2:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="B54" s="62"/>
-      <c r="C54" s="63"/>
-      <c r="D54" s="63"/>
-      <c r="E54" s="63"/>
-      <c r="F54" s="77" t="s">
+      <c r="B54" s="57"/>
+      <c r="C54" s="58"/>
+      <c r="D54" s="58"/>
+      <c r="E54" s="58"/>
+      <c r="F54" s="103" t="s">
         <v>104</v>
       </c>
-      <c r="G54" s="24" t="s">
+      <c r="G54" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="H54" s="63" t="s">
+      <c r="H54" s="58" t="s">
         <v>137</v>
       </c>
-      <c r="I54" s="100" t="s">
+      <c r="I54" s="79" t="s">
         <v>189</v>
       </c>
-      <c r="J54" s="101" t="s">
+      <c r="J54" s="80" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="55" spans="2:10" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B55" s="15"/>
-      <c r="C55" s="16"/>
-      <c r="D55" s="16"/>
-      <c r="E55" s="16"/>
-      <c r="F55" s="78"/>
-      <c r="G55" s="34" t="s">
+      <c r="B55" s="14"/>
+      <c r="C55" s="15"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="104"/>
+      <c r="G55" s="31" t="s">
         <v>173</v>
       </c>
-      <c r="H55" s="34" t="s">
+      <c r="H55" s="31" t="s">
         <v>192</v>
       </c>
-      <c r="I55" s="102" t="s">
+      <c r="I55" s="81" t="s">
         <v>190</v>
       </c>
-      <c r="J55" s="103" t="s">
+      <c r="J55" s="82" t="s">
         <v>191</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="F44:F46"/>
-    <mergeCell ref="G44:J44"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="G45:J45"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="F30:F32"/>
-    <mergeCell ref="G30:J30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="G31:J31"/>
     <mergeCell ref="F26:F27"/>
     <mergeCell ref="F33:F35"/>
     <mergeCell ref="F54:F55"/>
@@ -3893,6 +4010,21 @@
     <mergeCell ref="F9:F11"/>
     <mergeCell ref="F22:F23"/>
     <mergeCell ref="F13:F19"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="F30:F32"/>
+    <mergeCell ref="G30:J30"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="G31:J31"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="F44:F46"/>
+    <mergeCell ref="G44:J44"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="G45:J45"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="F2:F4"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D49" r:id="rId1" xr:uid="{1BDCDD1D-0819-496A-809D-C70FDD4A1FD8}"/>
